--- a/public/Excal-Student.xlsx
+++ b/public/Excal-Student.xlsx
@@ -1,19 +1,19 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29328"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29929"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Computer01\Downloads\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Computer01\Thitipong\CKK_School\Front-AdminCKK\public\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8152C2C7-E99A-45AB-A64E-FA884663E3C4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E1AA424E-A870-4F61-9A7C-0916B4C17497}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="3855" yWindow="2265" windowWidth="14400" windowHeight="13155" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="11190" yWindow="2790" windowWidth="14400" windowHeight="11145" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="ทำExcal ตัวอย่างให้หน่อย" sheetId="1" r:id="rId1"/>
+    <sheet name="Ex.Excal" sheetId="1" r:id="rId1"/>
   </sheets>
   <calcPr calcId="0"/>
 </workbook>
@@ -79,6 +79,7 @@
       <sz val="10"/>
       <color theme="1"/>
       <name val="Arial"/>
+      <family val="2"/>
       <scheme val="minor"/>
     </font>
   </fonts>

--- a/public/Excal-Student.xlsx
+++ b/public/Excal-Student.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Computer01\Thitipong\CKK_School\Front-AdminCKK\public\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{06E1BCC9-94B9-4D78-9E03-122F85B71EED}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CD94087E-08A3-4332-8488-D3086B1C6E91}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="23" uniqueCount="19">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="27" uniqueCount="21">
   <si>
     <t>นาย</t>
   </si>
@@ -77,6 +77,12 @@
   </si>
   <si>
     <t>เบอร์โทรผู้ปกครอง</t>
+  </si>
+  <si>
+    <t>-</t>
+  </si>
+  <si>
+    <t>รหัสบัตร (rfid)</t>
   </si>
 </sst>
 </file>
@@ -125,10 +131,16 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="5">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -347,10 +359,13 @@
   <sheetPr>
     <outlinePr summaryBelow="0" summaryRight="0"/>
   </sheetPr>
-  <dimension ref="A1:H4"/>
+  <dimension ref="A1:I4"/>
   <sheetFormatPr defaultColWidth="12.5703125" defaultRowHeight="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+  <cols>
+    <col min="7" max="7" width="16.5703125" customWidth="1"/>
+  </cols>
   <sheetData>
-    <row r="1" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A1" s="1" t="s">
         <v>8</v>
       </c>
@@ -373,10 +388,13 @@
         <v>18</v>
       </c>
       <c r="H1" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="I1" s="1" t="s">
         <v>14</v>
       </c>
     </row>
-    <row r="2" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A2" s="1">
         <v>1111</v>
       </c>
@@ -398,11 +416,14 @@
       <c r="G2">
         <v>1111111111</v>
       </c>
-      <c r="H2" s="2" t="s">
+      <c r="H2" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="I2" s="2" t="s">
         <v>15</v>
       </c>
     </row>
-    <row r="3" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A3" s="1">
         <v>2222</v>
       </c>
@@ -421,14 +442,17 @@
       <c r="F3" s="1">
         <v>1</v>
       </c>
-      <c r="G3">
-        <v>2222222222</v>
-      </c>
-      <c r="H3" s="2" t="s">
+      <c r="G3" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="H3">
+        <v>22222</v>
+      </c>
+      <c r="I3" s="2" t="s">
         <v>16</v>
       </c>
     </row>
-    <row r="4" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A4" s="1">
         <v>3333</v>
       </c>
@@ -450,7 +474,10 @@
       <c r="G4">
         <v>3333333333</v>
       </c>
-      <c r="H4" s="2" t="s">
+      <c r="H4" s="4" t="s">
+        <v>19</v>
+      </c>
+      <c r="I4" s="2" t="s">
         <v>17</v>
       </c>
     </row>
